--- a/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:41</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -499,7 +499,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>84.18</v>
+        <v>89.61</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>83.56</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="4">
@@ -533,7 +533,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>79.23</v>
+        <v>84.42</v>
       </c>
     </row>
     <row r="5">
@@ -550,7 +550,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>77.18</v>
+        <v>81.58</v>
       </c>
     </row>
     <row r="6">
@@ -567,7 +567,7 @@
         <v>2020</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>63.4</v>
+        <v>67.4</v>
       </c>
     </row>
     <row r="7">
@@ -584,7 +584,7 @@
         <v>2020</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>49.21</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="8">
@@ -601,7 +601,7 @@
         <v>2020</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>31.61</v>
+        <v>33.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_tarapaca.xlsx
@@ -63,7 +63,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:07</t>
+    <t xml:space="preserve">2026-10-05 16:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
